--- a/excel/Support_Ticket_Project.xlsx
+++ b/excel/Support_Ticket_Project.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC030B62-02F9-45E1-B93A-D5C29F9444B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABCEF003-9E83-43B8-AC47-FBA07FCA282A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,7 +14,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="596" r:id="rId4"/>
+    <pivotCache cacheId="204" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
   <si>
     <t>Ticket_ID</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Resolution_Days</t>
   </si>
   <si>
-    <t>2026--03-01</t>
-  </si>
-  <si>
     <t>ABC Ltd</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>Sara</t>
   </si>
   <si>
-    <t>2026--03-02</t>
-  </si>
-  <si>
     <t>YBD Ltd</t>
   </si>
   <si>
@@ -98,9 +92,6 @@
     <t>Aaish</t>
   </si>
   <si>
-    <t>2026--03-03</t>
-  </si>
-  <si>
     <t>NALEEM TREADERS</t>
   </si>
   <si>
@@ -113,9 +104,6 @@
     <t>Nshran</t>
   </si>
   <si>
-    <t>2026--03-04</t>
-  </si>
-  <si>
     <t>NAVO GROUP</t>
   </si>
   <si>
@@ -125,9 +113,6 @@
     <t>Shafee</t>
   </si>
   <si>
-    <t>2026--03-05</t>
-  </si>
-  <si>
     <t>SUN HR</t>
   </si>
   <si>
@@ -137,9 +122,6 @@
     <t>Dilani</t>
   </si>
   <si>
-    <t>2026--03-06</t>
-  </si>
-  <si>
     <t>Global Ltd</t>
   </si>
   <si>
@@ -149,9 +131,6 @@
     <t>Nimal</t>
   </si>
   <si>
-    <t>2026--03-07</t>
-  </si>
-  <si>
     <t>Clasic Creation</t>
   </si>
   <si>
@@ -161,9 +140,6 @@
     <t>Nimsha</t>
   </si>
   <si>
-    <t>2026--03-08</t>
-  </si>
-  <si>
     <t>TSK Ltd</t>
   </si>
   <si>
@@ -173,97 +149,64 @@
     <t>Arshd</t>
   </si>
   <si>
-    <t>2026--03-09</t>
-  </si>
-  <si>
     <t>Emit teil</t>
   </si>
   <si>
     <t>Fazriya</t>
   </si>
   <si>
-    <t>2026--03-10</t>
-  </si>
-  <si>
     <t>rolerl treand</t>
   </si>
   <si>
     <t>Zeineb</t>
   </si>
   <si>
-    <t>2026--03-11</t>
-  </si>
-  <si>
     <t>GHJ Ltd</t>
   </si>
   <si>
     <t>Tharushi</t>
   </si>
   <si>
-    <t>2026--03-12</t>
-  </si>
-  <si>
     <t>RTY Ltd</t>
   </si>
   <si>
     <t>Ruth</t>
   </si>
   <si>
-    <t>2026--03-13</t>
-  </si>
-  <si>
     <t>Boing Group</t>
   </si>
   <si>
     <t>Amash</t>
   </si>
   <si>
-    <t>2026--03-14</t>
-  </si>
-  <si>
     <t>Smsung</t>
   </si>
   <si>
     <t>Sajeewa</t>
   </si>
   <si>
-    <t>2026--03-15</t>
-  </si>
-  <si>
     <t>Camaye</t>
   </si>
   <si>
     <t>Frenando</t>
   </si>
   <si>
-    <t>2026--03-16</t>
-  </si>
-  <si>
     <t>Global Tarck</t>
   </si>
   <si>
     <t>Jeny</t>
   </si>
   <si>
-    <t>2026--03-17</t>
-  </si>
-  <si>
     <t>Samuyel Rec</t>
   </si>
   <si>
     <t>Nelon</t>
   </si>
   <si>
-    <t>2026--03-18</t>
-  </si>
-  <si>
     <t>Core Fen</t>
   </si>
   <si>
     <t>Geramy</t>
-  </si>
-  <si>
-    <t>2026--03-19</t>
   </si>
   <si>
     <t>criss Tof</t>
@@ -398,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -420,6 +363,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4827,189 +4771,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{50CF4A69-4917-4A7C-8464-2648DAC13FA9}" name="PivotTable2" cacheId="596" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="D14:E18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0">
-      <items count="21">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Ticket_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium10" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47B6917B-4F9D-4F00-843C-5A3EEB98C3D0}" name="PivotTable4" cacheId="596" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A14:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="9">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Resolution_Days" fld="7" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium12" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA4B6BA0-49B1-4506-B5EE-B5D4909F438E}" name="PivotTable3" cacheId="596" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA4B6BA0-49B1-4506-B5EE-B5D4909F438E}" name="PivotTable3" cacheId="204" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
   <location ref="D7:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
@@ -5160,8 +4922,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3C38B00-D500-4F66-9EA0-EFD989C4945D}" name="PivotTable1" cacheId="596" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3C38B00-D500-4F66-9EA0-EFD989C4945D}" name="PivotTable1" cacheId="204" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
@@ -5259,6 +5021,188 @@
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleMedium7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{50CF4A69-4917-4A7C-8464-2648DAC13FA9}" name="PivotTable2" cacheId="204" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="D14:E18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Ticket_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium10" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47B6917B-4F9D-4F00-843C-5A3EEB98C3D0}" name="PivotTable4" cacheId="204" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A14:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="9">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Resolution_Days" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium12" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -5653,23 +5597,23 @@
       <c r="A2">
         <v>1001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -5679,23 +5623,23 @@
       <c r="A3">
         <v>1002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -5705,23 +5649,23 @@
       <c r="A4">
         <v>1003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -5731,23 +5675,23 @@
       <c r="A5">
         <v>1004</v>
       </c>
-      <c r="B5" t="s">
-        <v>25</v>
+      <c r="B5" s="13">
+        <v>46085</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -5757,23 +5701,23 @@
       <c r="A6">
         <v>1005</v>
       </c>
-      <c r="B6" t="s">
-        <v>29</v>
+      <c r="B6" s="13">
+        <v>46086</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -5783,23 +5727,23 @@
       <c r="A7">
         <v>1006</v>
       </c>
-      <c r="B7" t="s">
-        <v>33</v>
+      <c r="B7" s="13">
+        <v>46087</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -5809,23 +5753,23 @@
       <c r="A8">
         <v>1007</v>
       </c>
-      <c r="B8" t="s">
-        <v>37</v>
+      <c r="B8" s="13">
+        <v>46088</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -5835,23 +5779,23 @@
       <c r="A9">
         <v>1008</v>
       </c>
-      <c r="B9" t="s">
-        <v>41</v>
+      <c r="B9" s="13">
+        <v>46089</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -5861,23 +5805,23 @@
       <c r="A10">
         <v>1009</v>
       </c>
-      <c r="B10" t="s">
-        <v>45</v>
+      <c r="B10" s="13">
+        <v>46090</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>11</v>
       </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -5887,23 +5831,23 @@
       <c r="A11">
         <v>1010</v>
       </c>
-      <c r="B11" t="s">
-        <v>48</v>
+      <c r="B11" s="13">
+        <v>46091</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -5913,23 +5857,23 @@
       <c r="A12">
         <v>1012</v>
       </c>
-      <c r="B12" t="s">
-        <v>51</v>
+      <c r="B12" s="13">
+        <v>46092</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H12">
         <v>9</v>
@@ -5939,23 +5883,23 @@
       <c r="A13">
         <v>1013</v>
       </c>
-      <c r="B13" t="s">
-        <v>54</v>
+      <c r="B13" s="13">
+        <v>46093</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -5965,23 +5909,23 @@
       <c r="A14">
         <v>1014</v>
       </c>
-      <c r="B14" t="s">
-        <v>57</v>
+      <c r="B14" s="13">
+        <v>46094</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -5991,23 +5935,23 @@
       <c r="A15">
         <v>1015</v>
       </c>
-      <c r="B15" t="s">
-        <v>60</v>
+      <c r="B15" s="13">
+        <v>46095</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
         <v>11</v>
       </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -6017,23 +5961,23 @@
       <c r="A16">
         <v>1016</v>
       </c>
-      <c r="B16" t="s">
-        <v>63</v>
+      <c r="B16" s="13">
+        <v>46096</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H16">
         <v>3</v>
@@ -6043,23 +5987,23 @@
       <c r="A17">
         <v>1017</v>
       </c>
-      <c r="B17" t="s">
-        <v>66</v>
+      <c r="B17" s="13">
+        <v>46097</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -6069,23 +6013,23 @@
       <c r="A18">
         <v>1018</v>
       </c>
-      <c r="B18" t="s">
-        <v>69</v>
+      <c r="B18" s="13">
+        <v>46098</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -6095,23 +6039,23 @@
       <c r="A19">
         <v>1019</v>
       </c>
-      <c r="B19" t="s">
-        <v>72</v>
+      <c r="B19" s="13">
+        <v>46099</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -6121,23 +6065,23 @@
       <c r="A20">
         <v>1020</v>
       </c>
-      <c r="B20" t="s">
-        <v>75</v>
+      <c r="B20" s="13">
+        <v>46100</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -6145,16 +6089,16 @@
     </row>
     <row r="21" spans="1:8">
       <c r="D21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H21">
         <v>7</v>
@@ -6190,16 +6134,16 @@
   <sheetData>
     <row r="1" spans="8:15" ht="54">
       <c r="H1" s="12" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="8:15" ht="26.25">
@@ -6256,12 +6200,12 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4">
         <v>3</v>
@@ -6269,7 +6213,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4">
         <v>2</v>
@@ -6277,7 +6221,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4">
         <v>2</v>
@@ -6285,7 +6229,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
@@ -6294,18 +6238,18 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4">
         <v>10</v>
@@ -6313,13 +6257,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" s="4">
         <v>9</v>
@@ -6327,13 +6271,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B10" s="4">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E10" s="4">
         <v>19</v>
@@ -6341,7 +6285,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4">
         <v>2</v>
@@ -6349,7 +6293,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B12" s="4">
         <v>19</v>
@@ -6360,24 +6304,24 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4">
         <v>5.666666666666667</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E15" s="4">
         <v>7</v>
@@ -6385,13 +6329,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4">
         <v>3.5</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E16" s="4">
         <v>6</v>
@@ -6399,13 +6343,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="4">
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="4">
         <v>6</v>
@@ -6413,13 +6357,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B18" s="4">
         <v>7.5</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E18" s="4">
         <v>19</v>
@@ -6427,7 +6371,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="4">
         <v>4.333333333333333</v>
@@ -6435,7 +6379,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
@@ -6443,7 +6387,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4">
         <v>4</v>
@@ -6451,7 +6395,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B22" s="4">
         <v>3.5</v>
@@ -6459,7 +6403,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B23" s="4">
         <v>4.4000000000000004</v>
